--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/159.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/159.xlsx
@@ -426,13 +426,13 @@
         <v>-12.06887765339207</v>
       </c>
       <c r="E2">
-        <v>-16.24397797777175</v>
+        <v>-16.43170133928572</v>
       </c>
       <c r="F2">
-        <v>0.7829586396327374</v>
+        <v>0.2652812000294227</v>
       </c>
       <c r="G2">
-        <v>-10.4133089022637</v>
+        <v>-9.63050392513871</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.4332285593553</v>
       </c>
       <c r="E3">
-        <v>-16.15838981902678</v>
+        <v>-17.5195947640444</v>
       </c>
       <c r="F3">
-        <v>0.5141343649740334</v>
+        <v>0.4058327823646232</v>
       </c>
       <c r="G3">
-        <v>-9.878361159118404</v>
+        <v>-9.742777766557552</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-10.81067415422867</v>
       </c>
       <c r="E4">
-        <v>-16.79656954703173</v>
+        <v>-17.23105851417167</v>
       </c>
       <c r="F4">
-        <v>0.7550476283628108</v>
+        <v>0.4840613147828001</v>
       </c>
       <c r="G4">
-        <v>-9.707685983841278</v>
+        <v>-9.806419694004502</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.28714813492609</v>
       </c>
       <c r="E5">
-        <v>-17.80370216633762</v>
+        <v>-18.50905727777236</v>
       </c>
       <c r="F5">
-        <v>0.5876296060526139</v>
+        <v>0.4019121194471732</v>
       </c>
       <c r="G5">
-        <v>-9.023419394692699</v>
+        <v>-9.476447688468724</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-9.868216553928931</v>
       </c>
       <c r="E6">
-        <v>-17.51867095534683</v>
+        <v>-18.77153215973093</v>
       </c>
       <c r="F6">
-        <v>0.7167704274142512</v>
+        <v>0.2618161391835124</v>
       </c>
       <c r="G6">
-        <v>-8.872352580644675</v>
+        <v>-9.505077286292343</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-9.562350293306258</v>
       </c>
       <c r="E7">
-        <v>-18.09570269882621</v>
+        <v>-19.09502370046887</v>
       </c>
       <c r="F7">
-        <v>0.633895582233772</v>
+        <v>0.5473394723152516</v>
       </c>
       <c r="G7">
-        <v>-8.592667761850429</v>
+        <v>-8.780326035744014</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-9.378342972337133</v>
       </c>
       <c r="E8">
-        <v>-18.30231885390018</v>
+        <v>-20.32691807019746</v>
       </c>
       <c r="F8">
-        <v>0.7353490515242386</v>
+        <v>0.8481229897413632</v>
       </c>
       <c r="G8">
-        <v>-8.354219098293342</v>
+        <v>-8.922136564464235</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-9.316956775242154</v>
       </c>
       <c r="E9">
-        <v>-19.78919800957867</v>
+        <v>-20.30231034243978</v>
       </c>
       <c r="F9">
-        <v>0.9313126145349064</v>
+        <v>0.8717977301133731</v>
       </c>
       <c r="G9">
-        <v>-8.034201903194154</v>
+        <v>-8.962111401850935</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-9.356804877462048</v>
       </c>
       <c r="E10">
-        <v>-18.63806444530287</v>
+        <v>-22.04003525882515</v>
       </c>
       <c r="F10">
-        <v>1.085427056356143</v>
+        <v>0.9647206718898105</v>
       </c>
       <c r="G10">
-        <v>-7.377475742386771</v>
+        <v>-7.786583028493286</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.494218299053076</v>
       </c>
       <c r="E11">
-        <v>-20.64068244876691</v>
+        <v>-21.70584293400709</v>
       </c>
       <c r="F11">
-        <v>1.317610155686817</v>
+        <v>1.283433373382115</v>
       </c>
       <c r="G11">
-        <v>-7.973059437629354</v>
+        <v>-8.145138284215131</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.69629713304875</v>
       </c>
       <c r="E12">
-        <v>-20.76721706948924</v>
+        <v>-23.36834536865105</v>
       </c>
       <c r="F12">
-        <v>1.509120415540034</v>
+        <v>1.156868774643184</v>
       </c>
       <c r="G12">
-        <v>-7.123795258803498</v>
+        <v>-7.956807969577071</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.934256851031185</v>
       </c>
       <c r="E13">
-        <v>-22.60301514745873</v>
+        <v>-22.73897352259101</v>
       </c>
       <c r="F13">
-        <v>1.667517516833745</v>
+        <v>1.493822126345133</v>
       </c>
       <c r="G13">
-        <v>-7.078497064189651</v>
+        <v>-7.138725819185612</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-10.19397442620865</v>
       </c>
       <c r="E14">
-        <v>-23.28030730546793</v>
+        <v>-24.22872825926437</v>
       </c>
       <c r="F14">
-        <v>1.755988812187537</v>
+        <v>2.0822346868409</v>
       </c>
       <c r="G14">
-        <v>-6.882671674450681</v>
+        <v>-7.652800572705798</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-10.4387302848031</v>
       </c>
       <c r="E15">
-        <v>-23.84025764499038</v>
+        <v>-23.92505784925801</v>
       </c>
       <c r="F15">
-        <v>1.775475326970993</v>
+        <v>1.972436244334631</v>
       </c>
       <c r="G15">
-        <v>-6.88522410506146</v>
+        <v>-7.253128341386206</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-10.65233172032939</v>
       </c>
       <c r="E16">
-        <v>-23.06742374236735</v>
+        <v>-25.62593910111697</v>
       </c>
       <c r="F16">
-        <v>2.248922089101828</v>
+        <v>2.263958614197445</v>
       </c>
       <c r="G16">
-        <v>-6.383904883504084</v>
+        <v>-7.021972809652135</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-10.82038786396289</v>
       </c>
       <c r="E17">
-        <v>-25.59345635705995</v>
+        <v>-25.4338412337116</v>
       </c>
       <c r="F17">
-        <v>1.559519945061162</v>
+        <v>2.506764697101619</v>
       </c>
       <c r="G17">
-        <v>-5.379700552349259</v>
+        <v>-6.522328724137631</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-10.92035003884907</v>
       </c>
       <c r="E18">
-        <v>-25.64086947992026</v>
+        <v>-27.46971635028797</v>
       </c>
       <c r="F18">
-        <v>2.868080334119902</v>
+        <v>2.758604954900725</v>
       </c>
       <c r="G18">
-        <v>-5.310536634942806</v>
+        <v>-6.560661530936851</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-10.95298266758614</v>
       </c>
       <c r="E19">
-        <v>-25.48997166903667</v>
+        <v>-28.19240646022407</v>
       </c>
       <c r="F19">
-        <v>2.797521655484245</v>
+        <v>3.223261082153051</v>
       </c>
       <c r="G19">
-        <v>-5.567411794971474</v>
+        <v>-5.888127515179449</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-10.91398857902002</v>
       </c>
       <c r="E20">
-        <v>-27.71734689444941</v>
+        <v>-28.67899099234825</v>
       </c>
       <c r="F20">
-        <v>2.963259748701565</v>
+        <v>3.567227392287101</v>
       </c>
       <c r="G20">
-        <v>-5.348488729005011</v>
+        <v>-5.430040707819416</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-10.80120362516168</v>
       </c>
       <c r="E21">
-        <v>-28.13891159677146</v>
+        <v>-29.48530163907299</v>
       </c>
       <c r="F21">
-        <v>3.227921477161201</v>
+        <v>3.636525295735697</v>
       </c>
       <c r="G21">
-        <v>-5.100886407031839</v>
+        <v>-5.779498584399344</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-10.632211925772</v>
       </c>
       <c r="E22">
-        <v>-27.61411127249655</v>
+        <v>-29.30299206823519</v>
       </c>
       <c r="F22">
-        <v>3.464761658030413</v>
+        <v>3.506552793501649</v>
       </c>
       <c r="G22">
-        <v>-4.349399190708358</v>
+        <v>-5.008575155214801</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-10.40929591748473</v>
       </c>
       <c r="E23">
-        <v>-29.25048441211625</v>
+        <v>-30.54642725397233</v>
       </c>
       <c r="F23">
-        <v>3.358795243129495</v>
+        <v>3.674595404833557</v>
       </c>
       <c r="G23">
-        <v>-4.668731102880918</v>
+        <v>-5.006909950808549</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-10.1448096882921</v>
       </c>
       <c r="E24">
-        <v>-29.36211582487933</v>
+        <v>-31.0034295296414</v>
       </c>
       <c r="F24">
-        <v>3.588675481080386</v>
+        <v>4.022406996451402</v>
       </c>
       <c r="G24">
-        <v>-3.966398866724536</v>
+        <v>-4.71187744289424</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-9.860159159836483</v>
       </c>
       <c r="E25">
-        <v>-30.1399333131478</v>
+        <v>-31.33033553978112</v>
       </c>
       <c r="F25">
-        <v>3.445674416335107</v>
+        <v>4.071061984222234</v>
       </c>
       <c r="G25">
-        <v>-3.35452066633766</v>
+        <v>-5.060269323810521</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-9.558547802837241</v>
       </c>
       <c r="E26">
-        <v>-30.04466554121144</v>
+        <v>-32.00122443554347</v>
       </c>
       <c r="F26">
-        <v>3.329205959501497</v>
+        <v>3.740599719488621</v>
       </c>
       <c r="G26">
-        <v>-2.625300179311317</v>
+        <v>-4.106325695032911</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-9.257988945861097</v>
       </c>
       <c r="E27">
-        <v>-29.61802441952679</v>
+        <v>-31.22234049164619</v>
       </c>
       <c r="F27">
-        <v>3.519142321289396</v>
+        <v>4.029559120607172</v>
       </c>
       <c r="G27">
-        <v>-3.621267873164436</v>
+        <v>-4.121014585590657</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-8.972475944078763</v>
       </c>
       <c r="E28">
-        <v>-31.64146208224111</v>
+        <v>-31.87663705864444</v>
       </c>
       <c r="F28">
-        <v>3.80680946925958</v>
+        <v>3.220277302768168</v>
       </c>
       <c r="G28">
-        <v>-4.193326831804958</v>
+        <v>-4.593929326421086</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-8.703768491541179</v>
       </c>
       <c r="E29">
-        <v>-31.02587264682342</v>
+        <v>-31.5320020727647</v>
       </c>
       <c r="F29">
-        <v>2.992529282512083</v>
+        <v>3.534578119473161</v>
       </c>
       <c r="G29">
-        <v>-3.154775590680194</v>
+        <v>-3.950975035057071</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.469540948221855</v>
       </c>
       <c r="E30">
-        <v>-30.58534269535724</v>
+        <v>-31.55460368653698</v>
       </c>
       <c r="F30">
-        <v>3.126887161776551</v>
+        <v>3.418666325534232</v>
       </c>
       <c r="G30">
-        <v>-3.529383681721964</v>
+        <v>-4.450211923470245</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.272370235402489</v>
       </c>
       <c r="E31">
-        <v>-29.27345283228316</v>
+        <v>-30.55336940462609</v>
       </c>
       <c r="F31">
-        <v>3.303616033694214</v>
+        <v>3.211579445038773</v>
       </c>
       <c r="G31">
-        <v>-3.637476304124708</v>
+        <v>-4.139162996236942</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-8.110292592914533</v>
       </c>
       <c r="E32">
-        <v>-29.41305210051761</v>
+        <v>-31.58835893179016</v>
       </c>
       <c r="F32">
-        <v>3.014802425238556</v>
+        <v>3.216712009466518</v>
       </c>
       <c r="G32">
-        <v>-4.041478729009667</v>
+        <v>-4.589261457210713</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.994869245791847</v>
       </c>
       <c r="E33">
-        <v>-29.56775156533064</v>
+        <v>-31.06181514502229</v>
       </c>
       <c r="F33">
-        <v>2.885661603876919</v>
+        <v>3.159915826860973</v>
       </c>
       <c r="G33">
-        <v>-2.668969585519843</v>
+        <v>-4.060530918588173</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.914352188438972</v>
       </c>
       <c r="E34">
-        <v>-30.97463975613764</v>
+        <v>-30.65311130888203</v>
       </c>
       <c r="F34">
-        <v>3.115947741855181</v>
+        <v>3.004108202068414</v>
       </c>
       <c r="G34">
-        <v>-3.361942909436706</v>
+        <v>-4.364015249264241</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.866157103193526</v>
       </c>
       <c r="E35">
-        <v>-29.76232877225522</v>
+        <v>-30.20759550753341</v>
       </c>
       <c r="F35">
-        <v>3.092786589272907</v>
+        <v>3.08076532152348</v>
       </c>
       <c r="G35">
-        <v>-4.149008558670735</v>
+        <v>-3.72313666995335</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.850434096860193</v>
       </c>
       <c r="E36">
-        <v>-28.55067215286691</v>
+        <v>-29.87163934208937</v>
       </c>
       <c r="F36">
-        <v>3.184062736652579</v>
+        <v>3.352864132525451</v>
       </c>
       <c r="G36">
-        <v>-4.100297191605899</v>
+        <v>-4.492802091832969</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.850332221537768</v>
       </c>
       <c r="E37">
-        <v>-28.56097443123435</v>
+        <v>-29.23973834329605</v>
       </c>
       <c r="F37">
-        <v>3.439952054316568</v>
+        <v>3.304152815771229</v>
       </c>
       <c r="G37">
-        <v>-3.440664371815036</v>
+        <v>-4.614630167678149</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.863089693564564</v>
       </c>
       <c r="E38">
-        <v>-27.28833285238475</v>
+        <v>-29.26874774778918</v>
       </c>
       <c r="F38">
-        <v>3.13534644969394</v>
+        <v>3.575048837304334</v>
       </c>
       <c r="G38">
-        <v>-4.526265086143922</v>
+        <v>-3.947058659684114</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.87978246762691</v>
       </c>
       <c r="E39">
-        <v>-28.59748298868419</v>
+        <v>-28.8705409143987</v>
       </c>
       <c r="F39">
-        <v>2.697037376055054</v>
+        <v>3.341861756681468</v>
       </c>
       <c r="G39">
-        <v>-3.764869407021402</v>
+        <v>-3.945188201454426</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.885123222349084</v>
       </c>
       <c r="E40">
-        <v>-26.83964259075675</v>
+        <v>-28.15851536075067</v>
       </c>
       <c r="F40">
-        <v>2.987728065045457</v>
+        <v>3.517369615047405</v>
       </c>
       <c r="G40">
-        <v>-3.544608880657072</v>
+        <v>-4.497728183595404</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-7.879711958267835</v>
       </c>
       <c r="E41">
-        <v>-25.97078692527508</v>
+        <v>-27.66211762545187</v>
       </c>
       <c r="F41">
-        <v>2.565239152065236</v>
+        <v>3.40990716861703</v>
       </c>
       <c r="G41">
-        <v>-3.881864086379246</v>
+        <v>-4.928350705161643</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-7.852894426292112</v>
       </c>
       <c r="E42">
-        <v>-25.80872642596258</v>
+        <v>-27.47314440511178</v>
       </c>
       <c r="F42">
-        <v>2.826055599041077</v>
+        <v>3.415462200420204</v>
       </c>
       <c r="G42">
-        <v>-4.785351690592824</v>
+        <v>-4.094397799454917</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-7.798227150692622</v>
       </c>
       <c r="E43">
-        <v>-24.13653758541622</v>
+        <v>-27.20540290788228</v>
       </c>
       <c r="F43">
-        <v>2.809824568150624</v>
+        <v>3.607174581919705</v>
       </c>
       <c r="G43">
-        <v>-4.651956568633431</v>
+        <v>-3.752762741984287</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-7.723257068223313</v>
       </c>
       <c r="E44">
-        <v>-25.77507533561158</v>
+        <v>-26.74670471869733</v>
       </c>
       <c r="F44">
-        <v>3.401840526848569</v>
+        <v>3.289371427835674</v>
       </c>
       <c r="G44">
-        <v>-3.702962205437031</v>
+        <v>-4.462530463421873</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-7.621227680352137</v>
       </c>
       <c r="E45">
-        <v>-24.29553230782552</v>
+        <v>-24.98194481248617</v>
       </c>
       <c r="F45">
-        <v>3.291977471684882</v>
+        <v>3.704938502798102</v>
       </c>
       <c r="G45">
-        <v>-3.000391610001821</v>
+        <v>-4.156857862144347</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-7.498977245895706</v>
       </c>
       <c r="E46">
-        <v>-24.21925016316631</v>
+        <v>-25.42607037231443</v>
       </c>
       <c r="F46">
-        <v>3.557689570011268</v>
+        <v>3.665425377684566</v>
       </c>
       <c r="G46">
-        <v>-4.679685698070367</v>
+        <v>-3.679768523388897</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.365695485777912</v>
       </c>
       <c r="E47">
-        <v>-23.49228064529297</v>
+        <v>-25.24233659640123</v>
       </c>
       <c r="F47">
-        <v>3.477051316818347</v>
+        <v>3.566360919983773</v>
       </c>
       <c r="G47">
-        <v>-4.222502669642555</v>
+        <v>-4.547952469971688</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.221309433542242</v>
       </c>
       <c r="E48">
-        <v>-22.94894527690467</v>
+        <v>-24.44092802278979</v>
       </c>
       <c r="F48">
-        <v>3.73395952638778</v>
+        <v>3.49762299289947</v>
       </c>
       <c r="G48">
-        <v>-4.017953992407606</v>
+        <v>-3.854595122772269</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.081056208526651</v>
       </c>
       <c r="E49">
-        <v>-23.18788567944538</v>
+        <v>-24.05223098481542</v>
       </c>
       <c r="F49">
-        <v>3.177117704347508</v>
+        <v>3.581196980167912</v>
       </c>
       <c r="G49">
-        <v>-2.719822875548588</v>
+        <v>-3.896622498393317</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.952982783424569</v>
       </c>
       <c r="E50">
-        <v>-21.24563676297759</v>
+        <v>-23.36935974682877</v>
       </c>
       <c r="F50">
-        <v>3.540620231309181</v>
+        <v>3.738215678103364</v>
       </c>
       <c r="G50">
-        <v>-4.864069842425614</v>
+        <v>-4.108941026008935</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.842110315913945</v>
       </c>
       <c r="E51">
-        <v>-21.8875071972988</v>
+        <v>-23.29500673209683</v>
       </c>
       <c r="F51">
-        <v>3.061295374088081</v>
+        <v>3.26919571137309</v>
       </c>
       <c r="G51">
-        <v>-5.025276857460425</v>
+        <v>-4.468535793030111</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.766778699280081</v>
       </c>
       <c r="E52">
-        <v>-20.16261597625116</v>
+        <v>-23.22671281558715</v>
       </c>
       <c r="F52">
-        <v>3.308978884259939</v>
+        <v>3.404531064172862</v>
       </c>
       <c r="G52">
-        <v>-3.097271414663053</v>
+        <v>-4.127205305749094</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.72763884830352</v>
       </c>
       <c r="E53">
-        <v>-20.06932035474514</v>
+        <v>-22.0284378368915</v>
       </c>
       <c r="F53">
-        <v>3.757425518174284</v>
+        <v>3.697522957808241</v>
       </c>
       <c r="G53">
-        <v>-4.172145961444701</v>
+        <v>-4.953196349433873</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.731285107918203</v>
       </c>
       <c r="E54">
-        <v>-20.12881997473192</v>
+        <v>-22.28647481432257</v>
       </c>
       <c r="F54">
-        <v>3.234364518820176</v>
+        <v>3.493757830598008</v>
       </c>
       <c r="G54">
-        <v>-4.540238898865185</v>
+        <v>-4.936640311191979</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.789195331290533</v>
       </c>
       <c r="E55">
-        <v>-20.1601026731769</v>
+        <v>-21.66072574746867</v>
       </c>
       <c r="F55">
-        <v>3.592920035652331</v>
+        <v>3.489153764573248</v>
       </c>
       <c r="G55">
-        <v>-4.221926634718722</v>
+        <v>-4.706199857294389</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.893267197812352</v>
       </c>
       <c r="E56">
-        <v>-18.85124688768796</v>
+        <v>-21.42947016531897</v>
       </c>
       <c r="F56">
-        <v>3.06356178730214</v>
+        <v>3.586876267081506</v>
       </c>
       <c r="G56">
-        <v>-5.306338863199009</v>
+        <v>-5.554702610646213</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.048719769284889</v>
       </c>
       <c r="E57">
-        <v>-18.99341380068476</v>
+        <v>-21.04060557380631</v>
       </c>
       <c r="F57">
-        <v>3.300247891834432</v>
+        <v>3.638773484866895</v>
       </c>
       <c r="G57">
-        <v>-4.31718758261125</v>
+        <v>-5.132406111111241</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.253812782661027</v>
       </c>
       <c r="E58">
-        <v>-19.42154931879194</v>
+        <v>-21.1796976529519</v>
       </c>
       <c r="F58">
-        <v>3.159395612132015</v>
+        <v>3.424325731630159</v>
       </c>
       <c r="G58">
-        <v>-4.469734210515327</v>
+        <v>-5.041905727704184</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.495904949912239</v>
       </c>
       <c r="E59">
-        <v>-19.00276057103659</v>
+        <v>-19.949981479221</v>
       </c>
       <c r="F59">
-        <v>3.201629095796345</v>
+        <v>3.708715858154868</v>
       </c>
       <c r="G59">
-        <v>-5.008118299930382</v>
+        <v>-5.248841308272947</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.77659667031332</v>
       </c>
       <c r="E60">
-        <v>-18.04723444152212</v>
+        <v>-20.65412748809569</v>
       </c>
       <c r="F60">
-        <v>3.26477222944214</v>
+        <v>3.714650282228524</v>
       </c>
       <c r="G60">
-        <v>-5.801238936955738</v>
+        <v>-4.98950310236306</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.082530288181005</v>
       </c>
       <c r="E61">
-        <v>-17.57176278461276</v>
+        <v>-19.49919906260146</v>
       </c>
       <c r="F61">
-        <v>3.140868346801001</v>
+        <v>3.67146583278578</v>
       </c>
       <c r="G61">
-        <v>-5.240932414979628</v>
+        <v>-5.397749646629365</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.402058259904761</v>
       </c>
       <c r="E62">
-        <v>-18.05937980881069</v>
+        <v>-19.59239505767932</v>
       </c>
       <c r="F62">
-        <v>3.089287565363481</v>
+        <v>3.740939350123769</v>
       </c>
       <c r="G62">
-        <v>-5.566137234938855</v>
+        <v>-5.825088107020647</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.735508561582366</v>
       </c>
       <c r="E63">
-        <v>-18.56698098880447</v>
+        <v>-19.14903028148435</v>
       </c>
       <c r="F63">
-        <v>2.999419642568569</v>
+        <v>3.466473065084597</v>
       </c>
       <c r="G63">
-        <v>-5.58423598740205</v>
+        <v>-5.220777813736546</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.063469165295894</v>
       </c>
       <c r="E64">
-        <v>-16.9812226031685</v>
+        <v>-18.18627670745363</v>
       </c>
       <c r="F64">
-        <v>3.614782308147015</v>
+        <v>3.635622375266645</v>
       </c>
       <c r="G64">
-        <v>-5.92546384777135</v>
+        <v>-5.707487597829117</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.381235786611418</v>
       </c>
       <c r="E65">
-        <v>-16.39270664960567</v>
+        <v>-19.36780991774291</v>
       </c>
       <c r="F65">
-        <v>3.199627760151182</v>
+        <v>3.604725927877029</v>
       </c>
       <c r="G65">
-        <v>-5.838125035354297</v>
+        <v>-6.203678784346161</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.683871507486012</v>
       </c>
       <c r="E66">
-        <v>-16.30127223091679</v>
+        <v>-19.6237909679745</v>
       </c>
       <c r="F66">
-        <v>3.000841121031773</v>
+        <v>3.666165938142669</v>
       </c>
       <c r="G66">
-        <v>-6.623095109261967</v>
+        <v>-5.481523001500623</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.953020001478448</v>
       </c>
       <c r="E67">
-        <v>-15.37536232141248</v>
+        <v>-18.31910137857261</v>
       </c>
       <c r="F67">
-        <v>3.189959055825706</v>
+        <v>3.482468839632656</v>
       </c>
       <c r="G67">
-        <v>-6.303581117084748</v>
+        <v>-6.17538355162201</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.18655760163029</v>
       </c>
       <c r="E68">
-        <v>-16.36496068936067</v>
+        <v>-18.61909466768474</v>
       </c>
       <c r="F68">
-        <v>3.442877847983256</v>
+        <v>3.388586648403777</v>
       </c>
       <c r="G68">
-        <v>-6.477354962986632</v>
+        <v>-5.422088777434087</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.37548300843017</v>
       </c>
       <c r="E69">
-        <v>-15.04293157298341</v>
+        <v>-19.00250697649216</v>
       </c>
       <c r="F69">
-        <v>3.054312236882481</v>
+        <v>3.249613105970909</v>
       </c>
       <c r="G69">
-        <v>-6.370997066446466</v>
+        <v>-6.294155993934442</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.50600451430766</v>
       </c>
       <c r="E70">
-        <v>-16.40026920119848</v>
+        <v>-18.40632431643435</v>
       </c>
       <c r="F70">
-        <v>2.874019728397974</v>
+        <v>3.490750856925845</v>
       </c>
       <c r="G70">
-        <v>-6.196379031432068</v>
+        <v>-5.807462762569568</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.58006565553897</v>
       </c>
       <c r="E71">
-        <v>-16.16929438443725</v>
+        <v>-17.61977366604208</v>
       </c>
       <c r="F71">
-        <v>2.475223779872625</v>
+        <v>3.243054092875543</v>
       </c>
       <c r="G71">
-        <v>-6.743244738518737</v>
+        <v>-6.581186913280333</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-10.58770185134027</v>
       </c>
       <c r="E72">
-        <v>-16.11489835465711</v>
+        <v>-17.87938655242781</v>
       </c>
       <c r="F72">
-        <v>2.722807885956147</v>
+        <v>2.866532943811472</v>
       </c>
       <c r="G72">
-        <v>-5.819463490149426</v>
+        <v>-6.857955141454483</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-10.52302969770192</v>
       </c>
       <c r="E73">
-        <v>-16.36724304026054</v>
+        <v>-18.3790810168042</v>
       </c>
       <c r="F73">
-        <v>2.822921056788884</v>
+        <v>2.873106867520089</v>
       </c>
       <c r="G73">
-        <v>-5.895278293544275</v>
+        <v>-6.431100020711934</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.39444199060878</v>
       </c>
       <c r="E74">
-        <v>-16.6767642386848</v>
+        <v>-17.95686874269905</v>
       </c>
       <c r="F74">
-        <v>2.636583122998746</v>
+        <v>2.87236133685757</v>
       </c>
       <c r="G74">
-        <v>-5.032983807475849</v>
+        <v>-6.404099211293639</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-10.19575802332615</v>
       </c>
       <c r="E75">
-        <v>-16.61385920624426</v>
+        <v>-18.45172679683525</v>
       </c>
       <c r="F75">
-        <v>2.666472275626558</v>
+        <v>2.844375772521391</v>
       </c>
       <c r="G75">
-        <v>-5.221294258840672</v>
+        <v>-6.123586756114573</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.934372746226755</v>
       </c>
       <c r="E76">
-        <v>-16.27125750519395</v>
+        <v>-18.39314192859802</v>
       </c>
       <c r="F76">
-        <v>2.635622216811499</v>
+        <v>3.052312557972123</v>
       </c>
       <c r="G76">
-        <v>-6.083767514368219</v>
+        <v>-5.212637182255478</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.622649638138437</v>
       </c>
       <c r="E77">
-        <v>-17.95940015966934</v>
+        <v>-19.39726764116281</v>
       </c>
       <c r="F77">
-        <v>2.373382634637648</v>
+        <v>2.647022209008826</v>
       </c>
       <c r="G77">
-        <v>-5.294761885448178</v>
+        <v>-5.291875089737934</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-9.261671334331918</v>
       </c>
       <c r="E78">
-        <v>-17.264315627284</v>
+        <v>-19.04729811290203</v>
       </c>
       <c r="F78">
-        <v>2.097264584997295</v>
+        <v>2.636644422186553</v>
       </c>
       <c r="G78">
-        <v>-4.652148580274709</v>
+        <v>-5.664099587991429</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.867153169012109</v>
       </c>
       <c r="E79">
-        <v>-16.16755997889231</v>
+        <v>-19.24587169813838</v>
       </c>
       <c r="F79">
-        <v>2.124537753367065</v>
+        <v>2.466554086634925</v>
       </c>
       <c r="G79">
-        <v>-5.458988118014804</v>
+        <v>-5.212806020077981</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.449854616519083</v>
       </c>
       <c r="E80">
-        <v>-19.33706157923083</v>
+        <v>-20.23173407503024</v>
       </c>
       <c r="F80">
-        <v>2.19018421330412</v>
+        <v>2.405283063319457</v>
       </c>
       <c r="G80">
-        <v>-4.726337905809777</v>
+        <v>-5.980197097172121</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-8.013098917123193</v>
       </c>
       <c r="E81">
-        <v>-19.25169531571224</v>
+        <v>-21.35951429884848</v>
       </c>
       <c r="F81">
-        <v>2.192627897142379</v>
+        <v>2.40735232509165</v>
       </c>
       <c r="G81">
-        <v>-4.997564280751186</v>
+        <v>-4.76352195330687</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.575791344988922</v>
       </c>
       <c r="E82">
-        <v>-20.26421229061325</v>
+        <v>-20.9865220087327</v>
       </c>
       <c r="F82">
-        <v>2.451774355434177</v>
+        <v>2.487457109677168</v>
       </c>
       <c r="G82">
-        <v>-5.063556695531018</v>
+        <v>-4.564856115495206</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.143259012374205</v>
       </c>
       <c r="E83">
-        <v>-21.14190300888389</v>
+        <v>-22.92903357669294</v>
       </c>
       <c r="F83">
-        <v>1.949584901161004</v>
+        <v>2.373959178349997</v>
       </c>
       <c r="G83">
-        <v>-4.248073323387885</v>
+        <v>-4.294232259841944</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.721540536841601</v>
       </c>
       <c r="E84">
-        <v>-22.2740396246975</v>
+        <v>-23.27678415268996</v>
       </c>
       <c r="F84">
-        <v>2.361450830567724</v>
+        <v>2.279387785441988</v>
       </c>
       <c r="G84">
-        <v>-4.265745015476515</v>
+        <v>-4.104471789530919</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.330291137221702</v>
       </c>
       <c r="E85">
-        <v>-22.03307046580135</v>
+        <v>-24.02502391297733</v>
       </c>
       <c r="F85">
-        <v>1.963690341295874</v>
+        <v>1.95946069733718</v>
       </c>
       <c r="G85">
-        <v>-4.705461605639132</v>
+        <v>-4.459113980425345</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.970794801975677</v>
       </c>
       <c r="E86">
-        <v>-23.49690874572881</v>
+        <v>-25.64105967582859</v>
       </c>
       <c r="F86">
-        <v>1.782894185430465</v>
+        <v>1.88468728535608</v>
       </c>
       <c r="G86">
-        <v>-3.652963036157419</v>
+        <v>-4.019695339361263</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.656168464940867</v>
       </c>
       <c r="E87">
-        <v>-25.94189978958015</v>
+        <v>-25.62668177085423</v>
       </c>
       <c r="F87">
-        <v>1.433657801879805</v>
+        <v>1.934742214037643</v>
       </c>
       <c r="G87">
-        <v>-3.685356724259187</v>
+        <v>-3.803380983279744</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-5.399747485202916</v>
       </c>
       <c r="E88">
-        <v>-26.56490912965941</v>
+        <v>-28.09645262447555</v>
       </c>
       <c r="F88">
-        <v>1.241029246032808</v>
+        <v>2.16448825646928</v>
       </c>
       <c r="G88">
-        <v>-3.688531537431348</v>
+        <v>-2.752968057487771</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.203087255387974</v>
       </c>
       <c r="E89">
-        <v>-28.72110580061959</v>
+        <v>-28.07365628632093</v>
       </c>
       <c r="F89">
-        <v>1.628001078250597</v>
+        <v>1.628875834227953</v>
       </c>
       <c r="G89">
-        <v>-3.468588823438788</v>
+        <v>-2.942953644895466</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.082709960393616</v>
       </c>
       <c r="E90">
-        <v>-29.67652551099488</v>
+        <v>-30.29375198976635</v>
       </c>
       <c r="F90">
-        <v>1.304975896059319</v>
+        <v>1.488934758668616</v>
       </c>
       <c r="G90">
-        <v>-2.874882207516972</v>
+        <v>-2.88311553427314</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.04337095650561</v>
       </c>
       <c r="E91">
-        <v>-29.65984034851362</v>
+        <v>-30.86722208843869</v>
       </c>
       <c r="F91">
-        <v>1.285656711491229</v>
+        <v>1.354069918553634</v>
       </c>
       <c r="G91">
-        <v>-2.27257148373859</v>
+        <v>-3.87684860988725</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.086492783932731</v>
       </c>
       <c r="E92">
-        <v>-32.21322268197556</v>
+        <v>-32.3155639303119</v>
       </c>
       <c r="F92">
-        <v>1.037580555170444</v>
+        <v>1.027996344320053</v>
       </c>
       <c r="G92">
-        <v>-2.729883623442433</v>
+        <v>-3.940281972965225</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.22525938312326</v>
       </c>
       <c r="E93">
-        <v>-33.28941226566141</v>
+        <v>-34.62807899554286</v>
       </c>
       <c r="F93">
-        <v>0.7374365373792934</v>
+        <v>0.8781016060486774</v>
       </c>
       <c r="G93">
-        <v>-2.201613250649852</v>
+        <v>-3.752736257619973</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.450518461933526</v>
       </c>
       <c r="E94">
-        <v>-35.79721097976213</v>
+        <v>-36.17188786220877</v>
       </c>
       <c r="F94">
-        <v>0.3186802479160872</v>
+        <v>0.6778404729522857</v>
       </c>
       <c r="G94">
-        <v>-3.090911856682113</v>
+        <v>-3.189112569013515</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.760837886443803</v>
       </c>
       <c r="E95">
-        <v>-37.36208630751173</v>
+        <v>-38.57687210243935</v>
       </c>
       <c r="F95">
-        <v>0.2448569733459981</v>
+        <v>0.4026294856179976</v>
       </c>
       <c r="G95">
-        <v>-3.353173274303177</v>
+        <v>-3.991585497187311</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-6.156991186923117</v>
       </c>
       <c r="E96">
-        <v>-39.29563602541079</v>
+        <v>-39.22536316575976</v>
       </c>
       <c r="F96">
-        <v>0.2977821950782613</v>
+        <v>-0.0828708505909731</v>
       </c>
       <c r="G96">
-        <v>-3.069380068494694</v>
+        <v>-3.123471072060846</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-6.612761223226006</v>
       </c>
       <c r="E97">
-        <v>-42.55355834498608</v>
+        <v>-41.67456569043824</v>
       </c>
       <c r="F97">
-        <v>-0.01698664920931442</v>
+        <v>-0.1763090368919517</v>
       </c>
       <c r="G97">
-        <v>-3.598339034759444</v>
+        <v>-3.656654294433706</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.128150165214741</v>
       </c>
       <c r="E98">
-        <v>-43.81868265698296</v>
+        <v>-43.33377139600461</v>
       </c>
       <c r="F98">
-        <v>-0.7275684910047583</v>
+        <v>-0.4049077904707117</v>
       </c>
       <c r="G98">
-        <v>-3.280145950252394</v>
+        <v>-3.937683194716898</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.667179417000447</v>
       </c>
       <c r="E99">
-        <v>-45.53077867472192</v>
+        <v>-45.86767449852255</v>
       </c>
       <c r="F99">
-        <v>-0.7298705240171381</v>
+        <v>-0.6116086517564667</v>
       </c>
       <c r="G99">
-        <v>-3.291097234896303</v>
+        <v>-4.008297131069552</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.226045988424405</v>
       </c>
       <c r="E100">
-        <v>-48.38278669814567</v>
+        <v>-47.73562247770949</v>
       </c>
       <c r="F100">
-        <v>-0.8633329381191805</v>
+        <v>-1.080375138061485</v>
       </c>
       <c r="G100">
-        <v>-5.14781007950547</v>
+        <v>-3.794280293592287</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.749592996672961</v>
       </c>
       <c r="E101">
-        <v>-48.65940853290421</v>
+        <v>-50.41630021552704</v>
       </c>
       <c r="F101">
-        <v>-1.32573507766849</v>
+        <v>-1.038617137286362</v>
       </c>
       <c r="G101">
-        <v>-3.763151233886521</v>
+        <v>-4.483052535219815</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.273010741675627</v>
       </c>
       <c r="E102">
-        <v>-51.25718689341884</v>
+        <v>-52.16164881790432</v>
       </c>
       <c r="F102">
-        <v>-1.756605412030236</v>
+        <v>-1.265216211954763</v>
       </c>
       <c r="G102">
-        <v>-3.676640057854286</v>
+        <v>-5.200557001582677</v>
       </c>
     </row>
   </sheetData>
